--- a/rmonize/data_proc_elem/DPE_NAKO_P2.xlsx
+++ b/rmonize/data_proc_elem/DPE_NAKO_P2.xlsx
@@ -437,7 +437,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>age_anth_fup</t>
+          <t>basis_age_fup</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">

--- a/rmonize/data_proc_elem/DPE_NAKO_P2.xlsx
+++ b/rmonize/data_proc_elem/DPE_NAKO_P2.xlsx
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>anthro_bmi</t>
+          <t>anthro_BMI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>gcal</t>
+          <t>a_nu_gcal</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
